--- a/WorkScripts/SynologyReader/Report.xlsx
+++ b/WorkScripts/SynologyReader/Report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,23 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A1" t="n">
+        <v>141537</v>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>AI in tNavigator. Kick-off session</t>
+          <t>"Моргает" окно Cross-Section при его вызове</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Созвон с пользователями. Обзор возможности использования AI/ML в тНавигатор.</t>
+          <t>Проверил и закрыл; Нужен перенос в прод</t>
         </is>
       </c>
     </row>
@@ -441,321 +439,304 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Berkine - 404 Models RFFM</t>
+          <t>AHM project follow up meetign with Relaince</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Обсуждение вопросов по проекту конвертации интегрированной модели</t>
+          <t>Созвон с Relaince</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>138935</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>E300, /rfdyn/users3/dmitrii.bevzenko/models.E300/Medco/GEOM_25.1/GELAM_GEOM.data ; TIME</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Не досчитался вариант без тюнинга, Reynaldi сделал сам такой же расчет. Тикет закроем когда падение исправят.; Работа с моделью. В свежих версиях модель падает. Пробую посчитать в 25.1. Далее попробую убрать уже имеющийся тюнинг.</t>
-        </is>
-      </c>
+          <t>Berkine - Nexus to tNavigator Conversion</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>107653</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ES на модели AkerBP Frøy</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Работа с проектом</t>
-        </is>
-      </c>
+          <t>Berkine Internal Meeting</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84399
-90073 </t>
-        </is>
+      <c r="A5" t="n">
+        <v>145195</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Edit folder в fluid proprties</t>
+          <t>E100, /rfdyn/users3/konstantin.vorobev/models.E100/KMG_NII_TDB/ECL_13NTG_N_CMB1PC.zip; TIME</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Закрыл</t>
+          <t>Работа с проектом. Перезапустил на v2 модели. Загрузил в ДМ, анализ что там есть.; Запустил в очереди расчет. Сегодня еще запустил ДС.; Работа с моделью</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135951</v>
+        <v>140813</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FAIL по сходимости и измененяи в расчетах моделей E100, E300 в пачке v25.4m-7524-ga955a20de1fe</t>
+          <t>E3, N:\german.nepotasov\models.E300\Polito\GEOTHERM_ Comp\GEOTHERM_ Comp.data; CRASH с GPU</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Отписался в тикет по модели</t>
+          <t>В мастере падать перестало. Надо в прод перенести.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A7" t="n">
+        <v>137407</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fwd: FW: Stream line and allocation factor for DP and DPDP model.</t>
+          <t>E300, N:\german.nepotasov\models.E300\RFD\co2store_thermal_2salt_1solid_1\co2store_thermal_2salt_1solid_1.data; CRASH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Созвон с Qatarenergy. Обсуждение вопросов по линиям тока. Ответы на вопросы, демонстрация возможностей ПО.</t>
+          <t>Попросил тестеров проверить, т.к. у меня не воспроизводится</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A8" t="n">
+        <v>142139</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Issue with tNav AHM module</t>
+          <t>E300, \\mskzfs3\polina.tsvetkova\models.E300\Rospan\EDFM\FORECAST_FEB2026\FORECAST_ACH_BU_VAR_1_CORR_ITER4_PROD_MOD_V17.data; CHECK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Работа с проектом; Проверка сети. Запустил с настройкой Honor System Constrains. Посмотрим как изменятся результаты.; С разницей дебитов разобрались. Остался вопрос с ошибками в расчете сети.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69605</v>
+        <v>107653</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MBA, поддержать CPIOPERS для WFIPIPR</t>
+          <t>ES на модели AkerBP Frøy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Проверка. ОТписался в тикет. Полино тоже проверяет.</t>
+          <t>Работа с проектом.; Работа с проектом. Подготовка к workshop.; Обсуждение с коллегами что делаем по проекту. Обсуждение плана для workshop.; С Митей обсудили новости по проекту. Лед тронулся (и мы вместе с ним). Надо подготовить несколько тестовых проектов. Начал смотреть что можно сделать.; Работа с проектом. Подготовил слайды к завтрашней встрече с Aker. Склеил с слайдами от Маши и Тимура.; Решили что нужно им передать еще раз последний вариант проекта. Искал какой вариант им лучше будет показать)) Работа с проектом</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137148</v>
+        <v>140535</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MD Нет режима просмотра заказанных графиков при постановке задачи на облако через MD</t>
+          <t>FAIL и зменения запасов моделей GEO в пачке v26.1-2413-g574ea0bcb455</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Пробовал воспроизвести поведение описанное тестерами. Не получилось. Жду комментария от автора; Локализовали баг. Написал в тикет + завел связанные</t>
+          <t>С Машей смотрели почему в модели стали отличатся запасы на 70%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>139525</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MD, "N:\valentin.dubinin\users\139525\RUBE2_ML_ver_3.1.zip", CHECK</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Сергей М. сказал что такого нет и надо 1) мат модель 2) указание от руководства что это делаем</t>
-        </is>
-      </c>
+          <t>Flat View</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>120055</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MD, продумать инструмент, который бы позволял соотносить имена кейсов в проекте с названиями папок в папке Models</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Смотрел что сделано. Обсудили с Владом и Марианной. Оставляем текщее поведение на время. В будущем возможно надо будет перенести проверку на этап открытия проекта.; Обсуждение с разработчиком. Проверка.; Вернул на доработку; Посмотрел, как сейчас, сделано. Обсудили с Марианной в чате.; Закрыл</t>
-        </is>
-      </c>
+          <t>Frøy Ensembles</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133479</v>
+        <v>69605</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MD, странная визуализация некоторых Блоков разломов (Fault Blocks)</t>
+          <t>MBA, поддержать CPIOPERS для WFIPIPR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Проверка. Проблема в вывернутой геометрии ячейки.</t>
+          <t>Проверка. ОТписался в тикет. Полино тоже проверяет.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137970</v>
+        <v>146273</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MD: WF "wells_log_fill_gaps" требует лицензию GD / MinD / Seis</t>
+          <t>MD SIM Расчет модели в MD отличается от SIM из за ошибки импорта VFPALIAS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>С Сергеем посмотрели что с проектом. Т.к. курс для ДМ, а пытаются использовать лицензию ДГ, то приняли решение поменять крус. Он поговорит с документацией.</t>
+          <t>Обсуждение сделанного с автором тикета, с Марией и Евгением.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136695</v>
+        <v>141708</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MD: Не отображаются существующие LGR в окне удаления LGR</t>
+          <t>MD Не записываются мнемоники при инициализации модели по курсу MDAHM1.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Тестеры проверили тикет. Тоже посмотрел что вышло. Можно закрыть.; Проверил, как сейчас, работает и как было в старых версиях. Нужно будет обсудить инициативной группой и решить что делать.; Обсуждение с гр поддержки, а потом с Артуром текущей реализации. Надо вернуть как было.</t>
+          <t>Отписался в тикете</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135443</v>
+        <v>99059</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MD: Нефизичные результаты при сглаживании 3D-свойств</t>
+          <t>MD, Поддержать правила стратегии для Аквиферов</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Закрыл</t>
+          <t>Вернули на доработку. Обсуждение с разработчиком.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133609</v>
+        <v>132304</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MD: добавить в Workflow получение данных c вкладки Definition</t>
+          <t>MD/GD: автоматически добавлять новое сечение по кнопке Create/Edit Cross-Section</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Вернул на доработку; Вернул в доработку</t>
+          <t>Проверил. Завел связанный. Закрыть не могу, т.к. есть открытая подзадача.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133256</v>
+        <v>142607</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MD: добавить в Workflow получение данных c вкладки Fluids</t>
+          <t>MD: Fail выполнения воркфлоу schedule_rule_vfp_numbers_for_producers()</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Вернул на доработку; Вернул в доработку; Проверка. Обсуждение с разработчиком вопросов по реализации.</t>
+          <t>Отписался в тикете</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126586</v>
+        <v>133609</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MD: добавить в Workflow получение данных c табличных вкладок на Cases</t>
+          <t>MD: добавить в Workflow получение данных c вкладки Definition</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Проверил и закрыл</t>
+          <t>Вернул на доработку. При детальной проверке вылезло много мелких недочетов.; Вернул в доработку; Нужен перенос в прод. При проверке выяснилось что прод не перенесли, хотя в тикете есть запись. Плюс обнаружилось что get_mapping_types возвращает странные значения. на это завел отдельный тикет.; Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98300</v>
+        <v>133256</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MD: сделать скрытие расчетов по специализации вместо лицензионной компоненты</t>
+          <t>MD: добавить в Workflow получение данных c вкладки Fluids</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Проверка списка из https://redmine.rfdyn.ru/issues/98300#note-49 и внесение правок в таблицу; Обсудили с Владом, Алексеем, Димой</t>
+          <t>Вернул на доработку; Проверил и закрыл; Нужен перенос в прод</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132047</v>
+        <v>139908</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MD: убрать (исправить) предупреждение при добавлении/изменении свойств в правиле Edit Grid Property</t>
+          <t>MD: добавить в Workflow получение данных c вкладки Project Manager Cases</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Обсудили с инициативной группой. Отписался в тикет.</t>
+          <t>Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A22" t="n">
+        <v>138883</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Meeting with Kirill Isakov</t>
+          <t>NE, oksana.esaulova\models.Nexus\Berkine\B404_HM24_07\Include\BBKS\BBKS_PR24_051.fcs; conversion (slave FC)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Обсуждение 132376</t>
+          <t>Работа с проектом; Модель выложил; Работа с моделью; Работа с проектом + обсуждение как делать мастер модель</t>
         </is>
       </c>
     </row>
@@ -770,50 +751,54 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Работа с проектом.; Работа с проектом. Нашел причину расхождения количества активных ячеек и порового объема. Запасы по нефти, воде сбились. По газу разьехались.</t>
+          <t>Работа с проектом; Конвертация истории закончена</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123502</v>
+        <v>147958</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Petrobras\\Ticket-123502\\ARG_Area_EV-3_ALL.dat</t>
+          <t>NE: PINCHOUT с опцией AND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Перевод в МД, работали с Денисом над устранением ошибок импорта</t>
+          <t>Закрыл</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A25" t="n">
+        <v>141460</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Planned 26.1 AHM</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>NE: конвертация PINCHOUT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>При проверке 143783 нашел грабли с MINDZEXT. Обойти смог только удалением слова из дампа. Написал Алексею, он смотрит мою модель и свои тесты.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A26" t="n">
+        <v>143783</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Planned 26.1 GUI</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>NE: конвертировать комбинацию CORTOL и OVER PV в MINPVV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Проверка сделанного на моей модели. У меня ответ поменялся. Нашел как сделать правильно, написал в тикете. Оксана тоже перепроверила на своей модели. Вернули в доработку.; Проверил на своей модели. Закрыл.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -823,7 +808,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Planned 26.1 Solver</t>
+          <t>Planned 26.2 AHM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -836,14 +821,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Planned 26.1 Storage</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Планирование</t>
-        </is>
-      </c>
+          <t>Planned 26.2 GUI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -853,55 +834,49 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Planned 26.1 Wells</t>
+          <t>Planned 26.2 Licenses</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>32190</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SIM: Подгрузка бинарников с именем модели , в котором есть точка</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Закрыл; Проверил несколько комбинаций. Падаем. Вернул на доработку; В мастере починили. В прод надо перенести.</t>
-        </is>
-      </c>
+          <t>Planned 26.2 Physics</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>117929</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>STARS\\2025-3\\Reliance_India\\UCG_9reac20250603\_LDI03ORItemp_6months_dateCTR2_1.data</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Снизить ошибку мат баланса, Расчеты и работа с логом. Обсудили варианты по модели с Денисом и Митей.</t>
-        </is>
-      </c>
+          <t>Planned 26.2 Storage</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>133278</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TW. Подготовить интегрированный проект для документации для курса на основе открытых данных для демонстрации TeamWork</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Тестировали работу TW. Завел тикеты. Обсуждения с Сашей и Владом найденных проблем.; Тестировали работу TW. Обсуждения с Сашей и Димой найденных проблем.; Работа с проектом; Тестировали работу TW. С Сашами прошлись по шагам того что будем показывать на созвоне с BP.; Проверка сдеаланного</t>
-        </is>
-      </c>
+          <t>Planned 26.2 Wells</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -911,12 +886,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Task_prority_Adviser_26.2</t>
+          <t>RE Interview</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Расставил приоритеты, Костя тоже еще посмотрит</t>
+          <t>RE Interview</t>
         </is>
       </c>
     </row>
@@ -928,227 +903,229 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Task_prority_GUI_MD_SIM_26.2</t>
+          <t>RTA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="n">
+        <v>145192</v>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Task_prority_Storage_26.1</t>
+          <t>Sim: VFPALIAS: Проблема с импортом vfp таблиц, если они не заданы на начальном шаге</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Обсудили с Евгением какие тесты надо сделать</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135216</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TW: если в проекте меняю подключенную стратегию в кейсе, то в админ проект это изменение не приезжает</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>С Сашей проверили. Закрыл</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135217</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TW: если в стратегии отключить правило, то это изменение не попадает в админский проект</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>С Сашей проверили. Закрыл</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135215</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TW: мапинг для грида, PVT, RP помечается как измененный при получении изменений хотя изменений в мапинге не было</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>С Сашей проверили. Проблема исправилась, перенос в прод будет в соседнем тикете. Закрыл.; Обсуждение с Марианной и Сашей как воспроизводить и какое поведение ожидаемое</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Task_priority_GUI_FS_26.3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Приоритеты</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Task_priority_Storage_26.3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Расстановка приоритетов</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Task_prority_Storage_26.2</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Расстановка приоритетов</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Team work</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>С Сашей посмотрели решенные тикеты. Вернули на доработку.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Technical interview for the role of Support Reservoir Engineer, Ahmedabad, India</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>UAE Projects (Integrated Modeling weekly internal session)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Обсуждение текущих задач по конвертациям моделей</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Uncertainty Modeling tNav with Reliance India</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Обсуждение с Reliance India вопросов по модели</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>55278</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Workflow — перемещение дерева для расчётов, адаптация окна расчётов под содержимое по кнопке</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Обсудили с Олегом, Владом и Данилой что нужно переделать. Дописал  тикет; Проверка исправлений. Обсуждение с разработчиком. Вернул на доработку.; Проверил и закрыл; Обсуждение с разработчиками</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
       <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>132867</v>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>В tnavctrl нужно добавить параметр отключающий запись исходных результатов если есть RPTUPSCALE</t>
+          <t>UGM СПБ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Проверил и закрыл</t>
+          <t>Доделать перевод третьей презентации.; Подготовка слайдов. Презентация по ИИ практически закончена. Осталось доделать перевод третьей презентации.; Перевод презентации; Перевод слайдов</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>18085</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>business trip</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>В модели с LGR и без отличаются запасы и поровые объемы</t>
+          <t>UGM Санкт-Петербург</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Проверка исправлений. Обсуждение с разработчиком.; Обсуждение с разработчиком. Выяснили что исправление делает не совсем то что нужно. Показал как воспроизвести.; Обсуждение с разработчиком вопросов; Обсуждение с Андреем Казаровым и Сергеем Парыгиным вопросов. Было решено сделанное вынести в отдельный тикет, а этот перенести.</t>
+          <t>Проведение конференции и вечернего банкета; Дорога в Санкт-Петербург. Подготовка конференции</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>16278</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>business trip</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>В модели сильно меняется ответ если считать на разном количестве процов/узлов</t>
+          <t>UGM Тюмень</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ситуация в целом не особо поменялась; Исправление ошибок. Перезапуск моделей.</t>
+          <t>Проведение конференции, консультаций и вечернего банкета; Дорога в Тюмень. Подготовка конференции</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A46" t="n">
+        <v>86911</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Встреча с ООО «СТС-ГеоСервис»</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>WD: обратный знак производных при расчёте интерполяции VFP-таблицы</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Посмотрел что проверили тестеры. Сравнил с 26.1. Запустил для проверки в 25.4 с тюнингом.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129019</v>
+        <v>141038</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Выгружать при экспорте модели информацию по разломам неструктурированной сетки</t>
+          <t>WF моделей MD и GEO в пачке 20260320-v26.1m-4543-g71dbacaa05e0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Проверка коммитов. Обсуждение функционала с Денисом и Андреем</t>
+          <t>Разбирательство с тем какие лицензии, когда забираются</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A48" t="n">
+        <v>108876</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ГДРП</t>
+          <t>WF, Поддержать отображение виджета расчета воркфлоу и adviser в окне AI-помощника</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Обсуждение вопросов</t>
+          <t>Проверил и закрыл.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A49" t="n">
+        <v>142420</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Геомеханика</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Workflow fail, fail и изменения в расчетах моделей GEO, MD в пачке v26.1m-6344-g1375a9c2df96</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Проверка модели за тестерами. Вернул в доработку.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1158,132 +1135,142 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Геомеханика 1D + 3D, конкурирование с Techlog</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>[Confirmed Time] tNav HM ensembles workshop</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>workshop для AkerBP по AHM</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>138501</v>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ДМ: не отключается режим создания полигона при закрытии окна редактирования</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Проверил и закрыл</t>
-        </is>
-      </c>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132582</v>
+        <v>142742</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Добавить Set-функции к траекториям скважин и стволов в хелпер Python</t>
+          <t>get_mapping_types возвращает только те типы данный у кейса которые не подсвечены красным</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Проверка. Обсуждение с Сашей и Олегом доработок.</t>
+          <t>Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>75101</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Добавить проект в пачку - тестирование расчетов SCHEDULE_IMPORT_MORES_FORMAT и SCHEDULE_EXPORT</t>
+          <t>tNav AHM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Проект подготовлен к добавлению в пачку. В табличку добавил.; Подготовка проекта</t>
+          <t>Созвон с AkerBP</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>73777</v>
+        <v>116952</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Добавить расчет создания EQUIL по контакту</t>
+          <t>В 25.2 на 4к мониторе не подсвечиваться результаты поиска в окне с мануалом</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Требует переноса в прод; Проверил. Нужен перенос в прод. На наклонном контакте проверить не смог из-за 134004. На горизонтальном все работает номально.; Проверил и вернул на доработку; Проверяю доработки; Обсуждение с Владиславом найденных недочетов.; Проверка сделанного. Обсуждение вопросов с разработчиком. Вернул на доработку.; Обсуждение с Владиславом найденных недочетов. Проверка сделанного. Обсуждение связанного тикета с обратной задачей.</t>
+          <t>Проверил и закрыл; Вернул на доработку</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>mail</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Домо по ИИ инструментам в тНавигатор</t>
+          <t>В ДГ разница в объемах при различных способах расчета</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Запланирован созвон на следующей неделе. Подготовка материалов к показу.</t>
+          <t xml:space="preserve">С Дашей разбирались в скрипте присланном пользователем. В итоге выяснилось что он сравнивает геометрический объем с эффективным. Отсюда идет разница в статистике. </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119689</v>
+        <v>143000</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Дополнительный тип данных в проекте GD/MD - база данных</t>
+          <t>В выдаче get_mapping_types упорядочить выдаваемый результат</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Вернул на доработку</t>
+          <t>Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A57" t="n">
+        <v>143444</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ежедневное собрание группы + RE2</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>В расчете Create Equilibration data by Contacts добавить возможность задавать переменные в качестве контактов</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Проверил и закрыл</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A58" t="n">
+        <v>140498</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ежедневное собрание группы + табличка</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>В расчете workflow "Constant Flux Aquifer Settings" добавить задание rainfall</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Проверил и закрыл</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>136892</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Замедление модели E100 в пачке v25.2m-9719-g64963f296c94</t>
+          <t>Встреча для обсуждения автоматизации для ЛИ в ПО тНавигатор</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1296,37 +1283,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Запрос на моделирование процесса образования вязкостной неустойчивости от Татнефти</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Обсуждение со специалистами Татнефть предлагаемых нами вариантов</t>
-        </is>
-      </c>
+          <t>Встреча с ООО «СТС-ГеоСервис»</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ключевые фичи 25.4</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Тестирование</t>
-        </is>
-      </c>
+          <t>ГРП в Новатэке</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business trips</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Командировка (Индия)</t>
+          <t>Геомеханика</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1339,273 +1322,259 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Круговые диаграммы в ДМ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>С Женей обсудили его предложения по доработке функционала по круговым диаграммам.</t>
-        </is>
-      </c>
+          <t>Геомеханика 1D + 3D, конкурирование с Techlog</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>133999</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ломается объект Contact если в сетке создать и удалить радиальный LGR</t>
+          <t>Гидрогеология</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>При проверке 73777 было не ясно почему ломается контакт. При пересоздании проекта все нормально. Разбирался почему так происходит и в итоге обнаружил что проблема в радиальных LGR. Завел тикет.</t>
+          <t>Обсуждение с гр GUI интерфейса для гидрогеологии</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A65" t="n">
+        <v>142619</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Мапинг переменных при вызове workflow из workflow</t>
+          <t>Глючит object filter в геометрических объектах</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Обсуждали с Ромой и Костей как упростить работу по заданию мапинга переменных</t>
+          <t>Вернул на доработку; Проверил. Обсудили с Васильевым. Завел #143206, этот закрыл.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>55024</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>На срабатывает ключ touch-after</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Проверка; Проверил и закрыл</t>
-        </is>
-      </c>
+          <t>Динамические сетки в горнорудной отрасли + Горнорудная геомеханика</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134004</v>
+        <v>140501</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Навигатор молча закрывается при запуске расчета по созданию контакта по горизонту</t>
+          <t>Добавить в AQUOPTS для AQUCHGAS опции DENY_BACKFLOW и DENY_INFLUX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Проверил и закрыл</t>
+          <t>Опция появилась. Обсудили с Алексеем в чате, решили сразу добавить опции для AQUCHWAT. Вернул на доработку.; Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>93154</v>
+        <v>140919</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Написать матмодель просачивания флюида через стенку карьера</t>
+          <t>Добавить в ДГ/ДМ возможность заполнять ползунок по времени датам не только из ГДМ, а еще и из произвольных таблиц</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Обсудили с разработчиками. Пока от меня ничего особо не требуется. Тикет в обратной связи потому что разработчику нужно обсудить вопрос с руководителем</t>
+          <t>Вернул на доработку; Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A69" t="n">
+        <v>141304</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Обсуждение 122073</t>
+          <t>Добавить в ДМ FlatView вариант отображения кейса (прототип)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>С Германом, Денисом, Андреем обсудили что именно нужно сделать и в каком виде</t>
+          <t>Работа с макетом. В итоге собрал в экселе, в тикет приложил скрин и эксельку.; Этот закрыл, завел новый сводный и часть тикетов на доделки.; По результатам встречи завел тикет. Подготовил примерный прототип FlatView вида. Обсуждение с GUI</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A70" t="n">
+        <v>133593</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Обсуждение 133278</t>
+          <t>Добавить в ДМ возможность задать AQSTREAZ в Fluid props</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>В свежем мастере проект падает. Отдали Владу посмотреть что происходит.</t>
+          <t>Вернул на доработку; Обсудили с Дарьей в чате. Нужно уточнение насколько доделки сложно реализовать. Жду комментария. ; Проверил и закрыл. Доработку вынес в отдельный тикет.; Проверил, вернул на доработку.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A71" t="n">
+        <v>139599</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Обсуждение по #132376</t>
+          <t>Добавить возможность создавать Groupset с выбранным набором вариантов</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Обсуждение вопросов. Изучение презентации</t>
+          <t>Вернул на доработку; Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A72" t="n">
+        <v>139947</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Обсуждение по экспорту UFAULTS</t>
+          <t>Добавить геттеры для Results Output</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Обсуждение по экспорту UFAULTS 129019, 120654. danil.kalinichenko, andrey.spiridonov, denis.luganskiy</t>
+          <t>Вернул на доработку; Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131408</v>
+        <v>140705</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Опция RPTUPSCALE пишет нулевые насыщенности</t>
+          <t>Добавить ключевое слово FAULTSDIP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Проверка; Закрыл</t>
+          <t>Написал что указываем в description в ДМ в этом тикете и в #140706</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A74" t="n">
+        <v>119509</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Организация работы в группе RE и GEO: первая и вторая линия. Взаимодействие с другими группами: с разработчиками, с группой тестирования, с документацией.</t>
+          <t>Добавление функционала фильтра с поиском для колонок таблиц.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Обучение новых сотрудников</t>
+          <t>Проверка сделанного</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>132869</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Отключать запись исходных результатов пр наличии RPTUPSCALE и параметра в TNAVCTRL</t>
+          <t>Дорожная карта развития tNavigator 2026-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Проверка; Выяснилось что у параметра невернуй дефолт. Поменяли.; Обсудили с Константином ожидаемое поведение. Закрыл.</t>
+          <t>Созвон с специалистами Алроса</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Оценка эффективности</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Заполнение формы самооценки</t>
-        </is>
-      </c>
+          <t>Ежедневное собрание группы + RE2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123809</v>
+        <v>20905</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ошибка записи файлов при расчёте на сетевом хранилище компании Perenco</t>
+          <t>Если из ДГ выгрузить recsue а потом загрузить обратно, то координаты ячеек отличаются.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Планируем созвон с пользователем. Смотрел что делалось по тикету.</t>
+          <t>Проверил в сежей версии. Закрыл.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>80878</v>
-      </c>
+      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Перенести галочку synchronize camera в раздел synchronization</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Проверил. Закрыл.</t>
-        </is>
-      </c>
+          <t>Заполнение формы самооценки</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A79" t="n">
+        <v>141575</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Перенос таблиц планирования в Redmine (#127835)</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Иконки ДМ: разработать иконку для логов у которых есть время</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Обсудили с Катей варианты</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Подготовка к India Energy Week</t>
+          <t>Ключевые фичи</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Обсуждение тем выступлений. Работа с презентациями.; Презентации.; Виза. Презентации.</t>
+          <t>С Денисом обсудили что включать в ключевые фичи</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1582,12 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Подготовка к встрече по ИИ с пользователем</t>
+          <t>Ключевые фичи 26.2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>При проверке подключения к ИИ серверу по логину пользователя нашел проблему. Жду решения от разработчиков. Готовлю вопросы/простые кейсы для демонстрации</t>
+          <t>Проверил. Тикеты закрыты.</t>
         </is>
       </c>
     </row>
@@ -1630,66 +1599,68 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Последняя пятница</t>
+          <t>Лаборатория СМА (интеграция данных цифрового керна)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A83" t="n">
+        <v>142622</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Предпланирование с GUI</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>Новый проект от компании Reliance: перенести данные из Petrel, воспроизвести модель и свойства, подготовить проект для гидродинамики, чтобы сделать интегрированный проект</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Работа с проектом; Нам дали ГДМ. Скачал, начал работать с моделью. Чуть позже соединим с геологией и соберем общий wf.; Работа с проектом.; Загрузил модель в ДМ. Работа с проектом.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135207</v>
+        <v>17637</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>При создании user проекта в TW есть проблемы с путями в windows</t>
+          <t>Нужна возможность брать в ДМ таблицы COMPVD напрямую из PVTD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Вернул в доработку; Проверил и закрыл</t>
+          <t>Вернул на доработку; Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131311</v>
+        <v>140925</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>При создании графика с типом well в APPLYSCRIPT не экспортируются результаты, если название графика начинается не с символа "W"</t>
+          <t>Нужна возможность отображать, редактировать дату у лога а табличном виде</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Попробовал найти в чем проблема потому что раньше не было зависимости от имен. В итоге нашлось, что проблема в логике скрипта. Вернул в обратную связь к автору.</t>
+          <t>Вернул на доработку; Обсуждение с Олегом; Проверил и закрыл; В целом то что получилось уже неплохо. Попросил геологов посмотреть. После этого закрою.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>137777</v>
+        <v>141843</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Проверить работу плагина при экспорте ГДМ из вкладка Cases в Petrel. Сейчас наблюдаются искажения траекторий скважин</t>
+          <t>Нужно сделать шаблон расположения иконки фильтра для таблиц (в ячейках с именами колонок)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Посмотрел причины. Нашлись лишние перфорации в ГДМ. Обсудили с Алиной. Тикет отменили.</t>
+          <t>Обсудили с Олегом варианты</t>
         </is>
       </c>
     </row>
@@ -1701,44 +1672,44 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Псевдонимы для объектов (#129771)</t>
+          <t>Обсуждение #101136</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>С Димой, Саше, Алексеем обсуждали реализацию</t>
+          <t>Обсуждение с гр GUI и Василием Ш.; Обсуждение с гр GUI как видим реализацию тикета</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>101443</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Рассчитать 10млрд. модель на кластере</t>
+          <t>Обсуждение #141304</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Работа с проектом</t>
+          <t>С гр GUI обсуждали реализацию тикета 141304</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>86517</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ревизия опции RUNCTRL REACRATECHOP</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Обсуждение с Денисом исходной модели. На UGM в Индии разговаривали с Reliance. Онип просили обновить статус по модели и по этому тикету.</t>
-        </is>
-      </c>
+          <t>Обсуждение 142234</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1748,44 +1719,40 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>СО2 визард</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Смотрели что получается. Обсуждение доработок.</t>
-        </is>
-      </c>
+          <t>Обсуждение 142234</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="n">
-        <v>59152</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Сделать пример воркфлоу по созданию отчета по модели</t>
+          <t>Обсуждение 98286</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Работа с проектом; Работа с workflow</t>
+          <t>С разработчиками и инициативной гр обсуждали вопросы по реализации</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
-        <v>119842</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Сделать таблицы в интерфейсе дизайнеров отличающиеся построчечно.</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
+          <t>Обсуждение Data Exchanger</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1795,12 +1762,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Собрание по TW</t>
+          <t>Обсуждение View Results в ДМ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>С гр поддержки и Владом смотрели работу TW. Обсуждали вопросы.</t>
+          <t>Созвон с инициативной группой</t>
         </is>
       </c>
     </row>
@@ -1812,14 +1779,10 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Совещаение</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>C Денисом, Андреем и геологами обсуждали реализацию функционала для Малазийского проекта</t>
-        </is>
-      </c>
+          <t>Обсуждение вопросов по 106942</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1829,14 +1792,10 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Совещание</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>обсуждение с Денисом проекта \\models.DISIGNER\\2026-1\\CCED\\SE_NSector2; последняя пятница месяца</t>
-        </is>
-      </c>
+          <t>Обсуждение вопросов по UFAULTS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1846,14 +1805,10 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Совещание по TW</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Обсуждали с гр. GUI доработки по TW</t>
-        </is>
-      </c>
+          <t>Обсуждение докладов на конференциях</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1863,7 +1818,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Совещание по Геомеханике</t>
+          <t>Обсуждение задач по петрофизике</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1876,59 +1831,49 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Совещание по Геомеханике</t>
+          <t>Обсуждение текущего состояния teamwork (+ND, +Сейсмика)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Созвон по презентации 132376</t>
+          <t>Подготовка к UGM</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>С Димой и Андреем обсудили что нужно сделать по презентации. Запланировали встречу на пятницу.</t>
+          <t>Работа с презентациями</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Созвон с Murphy по плагину</t>
+          <t>Подготовка презентаций к UGM</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Созвонились с Murphy, обсудили вопросы по плагину и по тикету 137777</t>
+          <t>Обновление презентаций к UGM в Тюмени</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Meetings</t>
-        </is>
+      <c r="A101" t="n">
+        <v>41743</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Созвон с Лилианой</t>
+          <t>Поддержать Drainage Network в ДМ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Обсуждение вопросов по WCONINJE с MULTI. Обсуждение вопросов по расстановке скважин.</t>
+          <t>Проверил. Нужен перенос в прод.</t>
         </is>
       </c>
     </row>
@@ -1940,155 +1885,296 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Созвон с гр GUI по текущим вопросам</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Созванивались с гр GUI, обсуждали вопросы по ряду тикетов</t>
-        </is>
-      </c>
+          <t>Предпланирование с GUI</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="n">
-        <v>93318</v>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Создание дождя</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Вернул на доработку</t>
-        </is>
-      </c>
+          <t>Презентация для круглого стола ГКЗ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="n">
-        <v>6665</v>
-      </c>
+      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Создать модель для тестирования у заказчиков</t>
+          <t>Презентация по планам развития</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Работа с проектом; Работа с проектом.; Работа с проектом. Найдено нескольо багов, заведены тикеты.</t>
+          <t>Подготовка слайдов</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>17882</v>
+        <v>18999</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Создать поверхности для флюидальных контактов из EQUIL tables</t>
+          <t>При последовательном создании LGR значения в кубе lgr_index сеъзжают</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Проверил и закрыл; Проверка сделанного. Закрыл.</t>
+          <t>Проверил в сежей версии. Закрыл.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134615</v>
+        <v>64633</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Через какое-то время в главном окне блокируются только два модуля</t>
+          <t>При правке закладки Fluid запускается расчет schedule</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Запустил проверку в свежей версии; Вернул на доработку; Оставлю мастер висеть на выходные. Если не заблокируется, то перенесем в прод.</t>
+          <t>Проверил и закрыл</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132376</v>
+        <v>135207</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>перенести ppt от автора в наш шаблон и научиться рассказывать эту презентацию (для будущих оффлай мероприятий или онлайн вебинаров)</t>
+          <t>При создании user проекта в TW есть проблемы с путями в windows</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Работа с презентацией</t>
+          <t>Проверил и закрыл; Проверка в проде. Закрыл.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127122</v>
+        <v>131900</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>подготовить вопросы для нашего ИИ и создать содержательные ответы в виде wf на 2 языках: RU и ENG (10 штук)</t>
+          <t>Расчет Create Radial LGR позволяет задать текст в поле Block Radii</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Поймал несколько падений. Уже исправлено. Надо проверить как версия соберется.; Закончил с подготовкой workflow. Осталось отправить ИИ</t>
+          <t xml:space="preserve">Вернул на доработку. Попутно завел тикет на еще одну багу.; Тикет зарыл. По согласованию с разработчиком вынес доработки в 147949 </t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>118823
-127122</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>подготовить вопросы для нашего ИИ и создать содержательные ответы в виде воркфлоу или текста (10 штук)</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Занес в "Обучающие примеры" все подготовленные вопросы
-</t>
-        </is>
-      </c>
+          <t>Режим просмотра результатов в MD</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="n">
-        <v>118823</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>подготовить вопросы для нашего ИИ и создать содержательные ответы в виде воркфлоу или текста (10 штук)</t>
+          <t>С гр GUI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Вношу старые вопрос/ответ в ИИ. Столкнулся с рядом проблем. Обход займет какое-то время</t>
+          <t>Прошлись по плановым тикетам, обсудили вопросы; Предпланирование. Обсуждение вопросов по тикетам.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Mail</t>
-        </is>
+      <c r="A111" t="n">
+        <v>101136</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>проверка релиз ноутс 25.4 по своим модулям</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Проверка, что в ДМ есть все интерфейсы</t>
-        </is>
-      </c>
+          <t>Сделать отдельный режим специализации для View Results Дизайнера Моделей</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Совещание по REStudio</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>С Денисом и Алексеем обсуждали как можем реализовать нечто похожее на REStudio. Посмотрели что сделано у конкурентов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Совещание по Геомеханике</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Совещание по таблице расчётов по геомеханике и петрофизике</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Созвон по поводу нового окна фильтров</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Обсуждение новых концептов от Кэми</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Созвон с ТИмуром, Костей, Сашей</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Обсудили PGS и APGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>93318</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Создание дождя</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Вернул на доработку</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Создать тикеты по релиз ноутс 26.1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Работа с таблицей, обсуждение с разработчиками, проверка тикетов, создание новых.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Табличка к планированию GUI</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>134615</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Через какое-то время в главном окне блокируются только два модуля</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>В 26.1 опять поймал после вчерашнего обновления сервера</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>135251</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>подготовить вопросы для нашего ИИ и создать содержательные ответы в виде wf на 2 языках: RU и ENG (10 штук)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Примеры подготовлены</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>140985</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>подготовить вопросы для нашего ИИ и создать содержательные ответы в виде текста/wf на 2 языках: RU и ENG (10 штук)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
